--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0030.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0030.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Archive: Discord</t>
+          <t>Lưu trữ: Tacet Discord</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Archive: Huaxu Academy, Jinzhou Campus</t>
+          <t>Lưu Trữ: Học viện Huaxu, Cơ sở Jinzhou</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Archive: Vắc-xin Sugar Pearl và Sự bùng phát Discord</t>
+          <t>Lưu Trữ: Sugar Pearl Vaccine and Tacet Discord Outbreak</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Archive: "The First Resonator"</t>
+          <t>Lưu Trữ: "Resonator Đầu Tiên"</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>"Suppressor Site 1 - Maintenance Log"</t>
+          <t>"Trạm Triệt Âm 1 - Nhật Ký Bảo Trì"</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>"Suppressor Site 2 - Maintenance Log"</t>
+          <t>"Trạm Triệt Âm 2 - Nhật Ký Bảo Trì"</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Unsent Message</t>
+          <t>Tin nhắn chưa gửi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Torn Diary 1</t>
+          <t>Nhật Ký Rách Nát - Phần 1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Torn Diary 2</t>
+          <t>Nhật Ký Rách - Phần 2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Torn Diary 3</t>
+          <t>Nhật Ký Rách - Phần 3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Torn Diary 4</t>
+          <t>Nhật Ký Rách - Phần 4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Torn Diary 5</t>
+          <t>Nhật Ký Rách - Phần 5</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Torn Diary 6</t>
+          <t>Nhật Ký Rách - Phần 6</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Torn Diary 7</t>
+          <t>Nhật Ký Rách - Phần 7</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Con Đường Cô Đơn</t>
+          <t>Con Đường Cô Độc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Last Wish</t>
+          <t>Ước Nguyện Cuối Cùng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Guide Ẩm Thực Michelin: Jinzhou Ngon Tuyệt - Khám Phá Ẩm Thực</t>
+          <t>Hướng Dẫn Ẩm Thực Michelin: Tasty Jinzhou - Food Exploration</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Guide Ẩm Thực Michelin: Jinzhou Ngon Tuyệt - Khám Phá Ẩm Thực</t>
+          <t>Hướng Dẫn Ẩm Thực Michelin: Tasty Jinzhou - Food Exploration</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>We Promise, We Deliver—Lollo Logistics</t>
+          <t>Lời Hứa Là Sẽ Giao—Lollo Logistics</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Refreshment Tea Distribution Thông báo</t>
+          <t>Thông báo phát Trà giải khát</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Energy Drink Poster</t>
+          <t>Áp Phích Nước Tăng Lực</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Gặp gỡ ở Jinzhou: Visit Cửa hàng Mahe</t>
+          <t>Gặp gỡ ở Jinzhou: Ghé thăm Cửa hàng Mahe</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Report Giám sát Hiệu suất Bất thường của Phổ C-001</t>
+          <t>Báo cáo Giám sát Hiệu suất Bất thường của Phổ C-001</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>test/&lt;i&gt;Hồ Sơ CSC - Rover&lt;/i&gt;</t>
+          <t>test/&lt;i&gt;Hồ Sơ CSC - Vận Mệnh Giả&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CSC Nghiên cứu Memo I</t>
+          <t>Biên Bản Nghiên Cứu CSC I</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Communication Log: That Child</t>
+          <t>Bản Ghi Liên Lạc: Đứa Trẻ Ấy</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CSC Nghiên cứu Memo II</t>
+          <t>Biên Bản Nghiên Cứu CSC II</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Biên Niên Sử Hồng Trấn&lt;/i&gt; Quyển XIX: Events Trọng Đại I</t>
+          <t>&lt;i&gt;Biên Niên Sử Hongzhen&lt;/i&gt; Quyển XIX: Sự Kiện Trọng Đại I</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Biên Niên Sử Hồng Trấn&lt;/i&gt; Quyển XIX: Events Trọng Đại II</t>
+          <t>&lt;i&gt;Biên Niên Sử Hongzhen&lt;/i&gt; Quyển XIX: Sự Kiện Trọng Đại II</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hongzhen Township Journal 3</t>
+          <t>Nhật Ký Thị Trấn Hoằng Trấn 3</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Hongzhen Township Journal 4</t>
+          <t>Nhật Ký Thị Trấn Hoằng Trấn 4</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hongzhen Township Journal 5</t>
+          <t>Nhật Ký Thị Trấn Hoằng Trấn 5</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Story of the Guqin&lt;/i&gt;</t>
+          <t>&lt;i&gt;Truyện về Đàn Cầm&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Rite of Offering: Volume I</t>
+          <t>Nghi Thức Dâng Tế: Quyển I</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Rite of Offering: Volume II</t>
+          <t>Nghi Thức Dâng Tế: Quyển II</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Rite of Offering: Volume III</t>
+          <t>Nghi Thức Dâng Tế: Quyển III</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Rite of Offering: Volume IV</t>
+          <t>Nghi Thức Dâng Tế: Quyển IV</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Performance Invitation Letter</t>
+          <t>Thư mời biểu diễn</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Exiles' Communication Records</t>
+          <t>Hồ Sơ Liên Lạc Dân Lưu Đày</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Xiaosheng's Wish</t>
+          <t>Ước Nguyện của Tiểu Sinh</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Heying's Wish</t>
+          <t>Ước nguyện của Heying</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mahn's Wish</t>
+          <t>Ước Nguyện Của Mahn</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Shabby Journal</t>
+          <t>Cuốn Nhật Ký Tả Tơi</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Diary I</t>
+          <t>Nhật ký I</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Diary I</t>
+          <t>Nhật ký I</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Diary II</t>
+          <t>Nhật ký II</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Wish Tag</t>
+          <t>Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Wish Tag</t>
+          <t>Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Wish Tag</t>
+          <t>Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Wish Tag</t>
+          <t>Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Wish Tag</t>
+          <t>Thẻ Nguyện Ước</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Observation Journal</t>
+          <t>Nhật Ký Quan Sát</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>A Researcher's Diary</t>
+          <t>Nhật Ký Nghiên Cứu</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Observation Journal</t>
+          <t>Nhật Ký Quan Sát</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>A Researcher's Diary</t>
+          <t>Nhật Ký Nghiên Cứu</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Observation Journal</t>
+          <t>Nhật Ký Quan Sát</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>A Researcher's Diary</t>
+          <t>Nhật Ký Nghiên Cứu</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Nghiên cứu Log</t>
+          <t>Biên Bản Nghiên Cứu</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Ogo's Diary</t>
+          <t>Nhật Ký Của Ogo</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Nghiên cứu Journal</t>
+          <t>Nhật Ký Nghiên Cứu</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament V</t>
+          <t>Dấu vết Núi Firmament V</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Ghi chú With Crooked Writing</t>
+          <t>Ghi chú viết nguệch ngoạc</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament II</t>
+          <t>Dấu vết Núi Firmament II</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament VII</t>
+          <t>Dấu vết Núi Firmament VII</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Traces Núi Firmament IX</t>
+          <t>Dấu vết Núi Firmament IX</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>An Adventurer's Diary</t>
+          <t>Nhật ký của một Nhà Thám hiểm.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Fuling's Letter</t>
+          <t>Thư của Fuling</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Bản ghi: Sự Rối Loạn Thời Gian và Quả Cầu Sonoro</t>
+          <t>Bản ghi: Temporal Disruption and Sonoro Sphere</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Ore Transaction Record</t>
+          <t>Biên Bản Giao Dịch Quặng</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Delivery Record</t>
+          <t>Hồ sơ giao hàng</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>List of Controlled Painters (Updating)</t>
+          <t>Danh sách Họa Sĩ Được Kiểm Soát (Đang cập nhật)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>//Excerpt from a personal journal//</t>
+          <t>//Trích từ nhật ký cá nhân//</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Nghiên cứu Memo–CT1946</t>
+          <t>Biên Bản Nghiên Cứu–CT1946</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Corrupted Log</t>
+          <t>Nhật Ký Đã Bị Nhiễm Độc</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Private Journal V</t>
+          <t>Nhật Ký Riêng Tập V</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Riddle Master's Hints</t>
+          <t>Gợi Ý Của Bậc Thầy Câu Đố</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Log</t>
+          <t>Nhật ký</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Zhezhi's Message</t>
+          <t>Lời nhắn của Zhezhi</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>A Short Ghi chú Left Behind</t>
+          <t>Một Mảnh Giấy Ghi Chú Vụn Vặt</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Error Cell Computer 3</t>
+          <t>Máy Tính Tế Bào Lỗi 3</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Bản Tường Trình Sự Cố Lament tại Port City of Guixu (Mười Một)</t>
+          <t>Bản Tường Trình Sự Cố Lament tại Thành Phố Cảng Guixu (Mười Một)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Resolution K626</t>
+          <t>Quyết Tâm K626</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Fragments of Quiet Reflections</t>
+          <t>Những Mảnh Suy Tư Lặng Lẽ</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Log Not Authorized for Review</t>
+          <t>Nhật Ký Không Được Phép Xem</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Report Điều tra về Cánh cổng tại Black Shores</t>
+          <t>Báo cáo Điều tra về Cánh cổng tại Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Audio Transcription</t>
+          <t>Bản Phiên Âm Âm Thanh</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Report Hệ thống Phân tích Stellar Matrix [RC-15407]</t>
+          <t>Báo cáo Hệ thống Phân tích Ma Trận Tinh Tú [RC-15407]</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>A Researcher’s Notes</t>
+          <t>Ghi Chép Nghiên Cứu</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>A Researcher's Notes</t>
+          <t>Ghi Chú Nghiên Cứu</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Fragment of Cold Instruction</t>
+          <t>Mảnh vỡ Chỉ dẫn Lạnh lẽo</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>The Tethys Hệ thống</t>
+          <t>Hệ Thống Tethys</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>The Black Shores Robots</t>
+          <t>Người Máy Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Stellar Matrix</t>
+          <t>Ma Trận Tinh Tú</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Anchor</t>
+          <t>Điểm Neo</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Oracle of Quercus</t>
+          <t>Lời Sấm của Quercus</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Sacred Path</t>
+          <t>Con Đường Thiêng</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Garden Nguyên Sơ</t>
+          <t>Vườn Nguyên Sơ</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Secret Game</t>
+          <t>Trò Chơi Bí Mật</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[Averardo Vault - Inventory Records]</t>
+          <t>Hồ sơ Kho Averardo - Biên bản Kiểm kê</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>To Do List</t>
+          <t>Danh Sách Việc Cần Làm</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Auctioneer Leaflet</t>
+          <t>Tờ Rơi Người Đấu Giá</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Placeholder</t>
+          <t>Vị trí tạm</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bloom Bearer Field Report</t>
+          <t>Báo Cáo Thực Địa Người Mang Hoa Nở</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>██livery██list</t>
+          <t>██lệnh██danh sách</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Deli██Check██</t>
+          <t>Giao██Kiểm██</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Yellowed Page</t>
+          <t>Trang Giấy Phai Màu</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Wrinkled Page</t>
+          <t>Trang Giấy Nhàu Nát</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>House Painter's Secret List</t>
+          <t>Bí Kíp Thợ Sơn Nhà</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Averardo Vault Important Thông báo (1)</t>
+          <t>Thông báo Quan trọng Hầm Averardo (1)</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Averardo Vault Important Thông báo (2)</t>
+          <t>Thông báo Quan trọng Hầm Averardo (2)</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Averardo Vault Important Thông báo (3)</t>
+          <t>Thông báo Quan trọng Hầm Averardo (3)</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vault Promotional Flyer</t>
+          <t>Tờ Rơi Quảng Cáo Kho Tàng</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Vault Tour Brochure (outdated)</t>
+          <t>Tờ Giới Thiệu Tham Quan Kho Tàng (lỗi thời)</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Work Log Nhân Viên</t>
+          <t>Nhật Ký Công Việc Nhân Viên</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Fallen Sticky Ghi chú</t>
+          <t>Mảnh Giấy Nhớ Sa Ngã</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Thông báo of Auction Suspension</t>
+          <t>Thông Báo Tạm Dừng Đấu Giá</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Nghiên cứu Log</t>
+          <t>Biên Bản Nghiên Cứu</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Experiment Record</t>
+          <t>Biên Bản Thí Nghiệm</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Grimy Sticky Ghi chú</t>
+          <t>Mảnh Giấy Nhớ Dính Bẩn</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Sheet of Paper</t>
+          <t>Tờ Giấy</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Confessions</t>
+          <t>Lời thú tội</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Damaged Log</t>
+          <t>Nhật Ký Hư Hỏng</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Tattered Log</t>
+          <t>Bản Ghi Chép Rách Nát</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Researcher's Message</t>
+          <t>Tin nhắn Nhà nghiên cứu</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Old Log</t>
+          <t>Khúc Gỗ Cũ</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>A Ghi chú Left by Carlotta</t>
+          <t>Lá Thư Carlotta Để Lại</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>The Lifer</t>
+          <t>Kẻ Tù Đày</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Black and White</t>
+          <t>Đen và Trắng</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Shackled Pieces</t>
+          <t>Mảnh Ghép Bị Xiềng Xích</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>&lt;i&gt;An Overclocker-proof Plan&lt;/i&gt;</t>
+          <t>&lt;i&gt;Kế hoạch chống lại Overclocker&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Ragunna City</t>
+          <t>Thành Phố Ragunna</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Pilgrim's Sail</t>
+          <t>Cánh Buồm Hành Hương</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Imperator</t>
+          <t>Đại Đế</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Common Echo</t>
+          <t>Tiếng Vọng Thường</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Genesis Nexus</t>
+          <t>Nexus Khởi Nguyên</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Dark Tide</t>
+          <t>Thủy Triều Bóng Tối</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Troupe of Fools</t>
+          <t>Đoàn Hội Ngớ Ngẩn</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Vượt Qua Đại Dương Vĩ Đại</t>
+          <t>Xuyên qua Đại Dương Ngươi Đi</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Act II</t>
+          <t>Hồi II</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Bỏ Màn Trong Nắng Hay Shadow</t>
+          <t>Bỏ Màn Trong Nắng Hay Bóng Tối</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Act III</t>
+          <t>Hồi III</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Act IV</t>
+          <t>Hồi IV</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Act V</t>
+          <t>Chương V</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Shadow Glory</t>
+          <t>Bóng Tối Vinh Quang</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Act VI</t>
+          <t>Chương VI</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Ngọn Lửa Trái Tim</t>
+          <t>Lửa Của Trái Tim</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Act VII</t>
+          <t>Chương VII</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Dreamcatcher tại Khu Vườn Bí Mật</t>
+          <t>Những Kẻ Bắt Giấc Mơ Trong Vườn Bí Mật</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Rinascita Chương II</t>
+          <t>Chương II: Rinascita</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Act VIII</t>
+          <t>Chương VIII</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Bằng Bàn Tay Cháy Bỏng Của Mặt Trời</t>
+          <t>Bởi Bàn Tay Rực Cháy của Mặt Trời</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Rinascita Chương II</t>
+          <t>Chương II: Rinascita</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Act IX</t>
+          <t>Hồi IX</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Even When Divinity Remains Silent</t>
+          <t>Dẫu Khi Thần Linh Im Lặng</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Blazing Guardians of Sacred Court</t>
+          <t>Hộ Pháp Rực Lửa của Tòa Thánh</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>The Quest Against Malevolence</t>
+          <t>Cuộc Chiến Chống Lại Ác Ý</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>See the Conquering Heroes Come</t>
+          <t>Hãy nhìn những Anh Hùng Chinh Phục trở về</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Thespian's Coronation</t>
+          <t>Lễ Đăng Quang của Thespian</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>From Dusk 'Til Darkness Falls</t>
+          <t>Từ Hoàng Hôn Đến Khi Bóng Tối Buông</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Crimson Curtain Call</t>
+          <t>Đại Kết Cục Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>The Unknown Wine List</t>
+          <t>Danh Sách Rượu Bí Ẩn</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Ordinary Wine List</t>
+          <t>Danh Sách Rượu Bình Thường</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Casually Jotted Down Snack List</t>
+          <t>Danh Sách Đồ Ăn Vặt Ghi Vội</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Perfect Curtain Call</t>
+          <t>Tiết Mục Hoàn Hảo</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Perfect Curtain Call</t>
+          <t>Tiết Mục Hoàn Hảo</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Averardo Vault Brochure&lt;/i&gt;</t>
+          <t>&lt;i&gt;Tờ giới thiệu Kho tàng Averardo&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Lonely SOL-3&lt;/i&gt;</t>
+          <t>&lt;i&gt;SOL-3 Cô Đơn&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Former Privy Councilor's Notes&lt;/i&gt;</t>
+          <t>&lt;i&gt;Ghi chép của Cựu Cố Vấn Cơ Mật Viện&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>&lt;i&gt;A Transgressor's Transcript&lt;/i&gt;</t>
+          <t>&lt;i&gt;Bản ghi của Kẻ Phạm Tội&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The Codex of Holy Rituals&lt;/i&gt;</t>
+          <t>&lt;i&gt;Bộ Kinh Nghi Lễ Thánh&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Essays on the Ragunnesi Drama&lt;/i&gt;</t>
+          <t>&lt;i&gt;Luận về Kịch nghệ Ragunnesi&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Voyage Logbook&lt;/i&gt;</t>
+          <t>&lt;i&gt;Nhật ký Hành trình&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Night Ngàn Sao</t>
+          <t>Đêm Ngàn Sao</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Data File Segment</t>
+          <t>Phân đoạn tập tin dữ liệu</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Một Page Nhật Ký Lạc Mất</t>
+          <t>Một Trang Nhật Ký Lạc Mất</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Một Page Nhật Ký Lạc Mất</t>
+          <t>Một Trang Nhật Ký Lạc Mất</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Một Page Nhật Ký Lạc Mất</t>
+          <t>Một Trang Nhật Ký Lạc Mất</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Echoes from an Unknown Source</t>
+          <t>Echo từ Nguồn không xác định</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A Sealed Confession: Part 1</t>
+          <t>Lời Thú Tội Bị Niêm Phong: Phần 1</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>A Sealed Confession: Part 2</t>
+          <t>Lời Thú Tội Bị Niêm Phong: Phần 2</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>A Sealed Confession: Part 3</t>
+          <t>Lời Thú Tội Bị Niêm Phong: Phần 3</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>A Message Viết Chưa Lâu</t>
+          <t>Một Tin Nhắn Viết Chưa Lâu</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>A Letter Possibly from Ahab</t>
+          <t>Một Bức Thư Có Thể Từ Ahab</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Ngày of Reckoning</t>
+          <t>Ngày Thanh Toán</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Impromptu Performance</t>
+          <t>Buổi Biểu Diễn Ứng Tác</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Repeat Performance</t>
+          <t>Lặp Lại Biểu Diễn</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>A Young Acolyte's Letter</t>
+          <t>Lá Thư Của Một Tiểu Tăng Trẻ</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Weathered Stele</t>
+          <t>Bia Đá Mòn Mỏi</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Divinity of Septimont</t>
+          <t>Thần Tính của Septimont</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Fisalia Knight's Letter</t>
+          <t>Thư của Hiệp sĩ Fisalia</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Small Paper Slip</t>
+          <t>Mảnh Giấy Nhỏ</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Small Paper Slip</t>
+          <t>Mảnh Giấy Nhỏ</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Small Paper Slip</t>
+          <t>Mảnh Giấy Nhỏ</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Picture Book</t>
+          <t>Sách Tranh</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tin Nhắn Trong Picture Book</t>
+          <t>Tin Nhắn Trong Sách Tranh</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Small Paper Slip</t>
+          <t>Mảnh Giấy Nhỏ</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Small Paper Slip</t>
+          <t>Mảnh Giấy Nhỏ</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Picture Book</t>
+          <t>Sách Tranh</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Tin Nhắn Trong Picture Book</t>
+          <t>Tin Nhắn Trong Sách Tranh</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Translated by a Kind Stranger</t>
+          <t>Được dịch bởi một người lạ tốt bụng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>SOS...</t>
+          <t>CỨU...</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Worn Notes</t>
+          <t>Ghi Chú Cũ Kỹ</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ciaccona's Letter kẹp trong cuốn sách</t>
+          <t>Lá thư của Ciaccona kẹp trong cuốn sách</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>"The Golden Anthem Anthology"</t>
+          <t>"Tuyển Tập Thánh Ca Vàng"</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>"Cultural Insights"</t>
+          <t>"Góc Nhìn Văn Hóa"</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>"Scattered Journal Pages"</t>
+          <t>"Những Trang Nhật Ký Rải Rác"</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Manuscripts Excerpt</t>
+          <t>Trích Đoạn Bản Thảo</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Giấc Mơ Đêm Thoáng Qua</t>
+          <t>Giấc Mộng Đêm Thoáng Qua</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Companion Story</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 1&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 1&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 7&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi chú của Sumika - Mục 7&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 136&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 136&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 159&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 159&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 160&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 160&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 161&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 161&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sumika's Notes - Entry 162&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chép của Sumika - Mục 162&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Report Nghiên cứu Dự án Sonoro Có thể Điều khiển Số 20&lt;/b&gt;</t>
+          <t>&lt;b&gt;Báo cáo Nghiên cứu Dự án Sonoro Có thể Điều khiển Số 20&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Report Nghiên cứu Dự án Sonoro Có thể Điều khiển Số 20&lt;/b&gt;</t>
+          <t>&lt;b&gt;Báo cáo Nghiên cứu Dự án Sonoro Có thể Điều khiển Số 20&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Record of the Knighting Ceremony</t>
+          <t>Bản ghi lễ phong hiệp sĩ</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Titular Repository Memoir (Excerpt)</t>
+          <t>Hồi Ký Kho Danh Hiệu (Trích Đoạn)</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Thông báo Tăng Cường Quản Lý Âm Thanh Dragon</t>
+          <t>Thông Báo Tăng Cường Quản Lý Âm Thanh Rồng</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>The Fisalias in Avinoleum (Excerpt)</t>
+          <t>Gia tộc Fisalia ở Avinoleum (Trích đoạn)</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Waterlogged Notes</t>
+          <t>Ghi chép ngâm nước</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Audio Log 4</t>
+          <t>Nhật Ký Âm Thanh 4</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Scribbled Notes</t>
+          <t>Ghi Chú Grib Grib</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>A Left-behind Ghi chú</t>
+          <t>Một Mảnh Giấy Bị Bỏ Lại</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Torn Pages of a Journal</t>
+          <t>Những Trang Nhật Ký Rách</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Living Quarters Memo</t>
+          <t>Bản Ghi Chú Nơi Ở</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Audio Log 1</t>
+          <t>Bản ghi âm số 1</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Sticker on Dartboard</t>
+          <t>Sticker trên Bảng Phi Tiêu</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Drinks Menu</t>
+          <t>Danh sách đồ uống</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Audio Log 2</t>
+          <t>Nhật Ký Âm Thanh 2</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Audio Log 3</t>
+          <t>Nhật Ký Âm Thanh 3</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Ancient Inscriptions</t>
+          <t>Bia Đá Cổ Xưa</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Titular Repository Memoir</t>
+          <t>Hồi Ký Kho Danh Hiệu</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Wuthering Waves</t>
+          <t>Sóng Gió Mạnh Mẽ</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Assured Victory</t>
+          <t>Chiến thắng chắc chắn</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Leonidas Hotel</t>
+          <t>Khách sạn Leonidas</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Central Hub</t>
+          <t>Trung Tâm Điều Hành</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>A Strange Ghi chú</t>
+          <t>Một Mảnh Giấy Ghi Chú Kỳ Lạ</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Message from "Conqueror of Prestige"</t>
+          <t>Tin Nhắn từ "Kẻ Chinh Phục Danh Vọng"</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Her Oath</t>
+          <t>Lời Thề Của Nàng</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Her Wishes</t>
+          <t>Những Điều Ước Của Nàng</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The Septimont Tribune&lt;/i&gt; Special Issue</t>
+          <t>&lt;i&gt;Tạp Chí Septimont&lt;/i&gt; Số Đặc Biệt</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>&lt;i&gt;The Gladiator&lt;/i&gt; Special Issue</t>
+          <t>&lt;i&gt;Ấn phẩm Đặc biệt: &lt;i&gt;Đấu Sĩ&lt;/i&gt;&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>The Great Agon Schedule</t>
+          <t>Lịch Trình Đại Khổ Nạn</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Daily Scoop</t>
+          <t>Tin Tức Hằng Ngày</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Guide Du Hành Qua Septimont</t>
+          <t>Hướng Dẫn Du Hành Qua Septimont</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Ecological Field Notes on Scourgewings</t>
+          <t>Ghi chép thực địa về Sinh thái của Scourgewings</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Record of a Duel</t>
+          <t>Bản ghi cuộc đấu tay đôi</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Letter from the Past</t>
+          <t>Lá Thư Từ Quá Khứ</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Work Log 1</t>
+          <t>Nhật Ký Công Việc 1</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Work Log 2</t>
+          <t>Nhật Ký Công Việc 2</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Work Log 3</t>
+          <t>Nhật Ký Công Việc 3</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Someone's Ghi chú I</t>
+          <t>Ghi Chú Của Ai Đó I</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Someone's Ghi chú II</t>
+          <t>Ghi Chú Của Ai Đó II</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Martialism</t>
+          <t>Chủ nghĩa võ biền</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Willpower</t>
+          <t>Ý Chí</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Reputation</t>
+          <t>Danh Tiếng</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Kiếm Glory</t>
+          <t>Kiếm Vinh Quang</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Nameless Girl: Augusta</t>
+          <t>Cô Gái Vô Danh: Augusta</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Trainee Gladiator: Augusta</t>
+          <t>Võ Sĩ Tập Sự: Augusta</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Fearless Trialbearer: Augusta</t>
+          <t>Người Thử Thách Dũng Cảm: Augusta</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Kiếm Glory: Augusta</t>
+          <t>Kiếm Vinh Quang: Augusta</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Summit of Septimont: Augusta</t>
+          <t>Đỉnh Septimont: Augusta</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ragunna Echoes Archive</t>
+          <t>Lưu Trữ Echoes Ragunna</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>"Project Echo Reborn" Meeting Record</t>
+          <t>"Biên bản họp Dự án Echo Tái Sinh"</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Test View Ghi chú 1</t>
+          <t>Ghi chú xem thử 1</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Test View Ghi chú 2</t>
+          <t>Ghi chú xem thử 2</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Test View Progress 1</t>
+          <t>Tiến độ xem thử 1</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Dừng lại</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Acis's letter</t>
+          <t>Lá thư của Acis</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Inspect vật phẩm</t>
+          <t>Kiểm tra vật phẩm</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Bỏ qua</t>
+          <t>Bỏ Qua</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Complete investigation</t>
+          <t>Hoàn thành điều tra</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Lá Thư Từ Ephor's Palace</t>
+          <t>Lá Thư Từ Cung Điện Ephor</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>How to Fight Kerasaurs IX</t>
+          <t>Cách chiến đấu với Kerasaurs IX</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Peso's Challenge Ghi chú</t>
+          <t>Bản Ghi Thử Thách của Peso</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Ghi chú from an Unknown Source&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chú Từ Nguồn Không Xác Định&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Ghi chú from an Unknown Source&lt;/b&gt;</t>
+          <t>&lt;b&gt;Ghi Chú Từ Nguồn Không Xác Định&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>&lt;b&gt;A Record Left Behind&lt;/b&gt;</t>
+          <t>&lt;b&gt;Bản Ghi Chép Bị Lãng Quên&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Peso's Memo Ghi chú</t>
+          <t>Bản Ghi Chú của Peso</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>A Letter with Nobility Seal</t>
+          <t>Một Bức Thư Đóng Dấu Quý Tộc</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Notes Left Behind</t>
+          <t>Những Ghi Chú Còn Lại</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Rinascita Chương II</t>
+          <t>Chương II: Rinascita</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Act X</t>
+          <t>Chương X</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dawn Trên Bóng Tối Dâng Trào</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Rinascita Chương II</t>
+          <t>Chương II: Rinascita</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Act XI</t>
+          <t>Chương XI</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Dawn Trên Bóng Tối Dâng Trào</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Dawn Trên Bóng Tối Dâng Trào</t>
+          <t>Bình Minh Trên Bóng Tối Dâng Trào</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Rinascita Chương II</t>
+          <t>Chương II: Rinascita</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Kẻ Lạ Mặt Ở Land Lạ</t>
+          <t>Kẻ Lạ Mặt Ở Vùng Đất Lạ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Kẻ Lạ Mặt Ở Land Lạ</t>
+          <t>Kẻ Lạ Mặt Ở Vùng Đất Lạ</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Chronorift Metropolis Chương II</t>
+          <t>Đô Thị Dị Thời Gian Chương II</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Act XII</t>
+          <t>Chương XII</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Dawn Trì Trệ trên Vùng Đất Hoang</t>
+          <t>Bình Minh Trì Trệ trên Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Dawn Trì Trệ trên Vùng Đất Hoang</t>
+          <t>Bình Minh Trì Trệ trên Vùng Đất Hoang</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Chronorift Metropolis Chương II</t>
+          <t>Đô Thị Dị Thời Gian Chương II</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Starlight Chảy Trong Mống Mắt</t>
+          <t>Ánh Sao Chảy Trong Mống Mắt</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Starlight Chảy Trong Mống Mắt</t>
+          <t>Ánh Sao Chảy Trong Mống Mắt</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Stele Inscription</t>
+          <t>Bia Đá Khắc</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>"Controllable Sonoro Project" Test Log</t>
+          <t>"Nhật Ký Thử Nghiệm Dự Án Sonoro Có Thể Điều Khiển"</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Guestbook</t>
+          <t>Sổ lưu bút</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Tổng Hợp Side Quests</t>
+          <t>Tổng Hợp Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Voices Along the Way</t>
+          <t>Lahai-Roi: Những Âm Thanh Dọc Đường</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Voices Along the Way</t>
+          <t>Lahai-Roi: Những Âm Thanh Dọc Đường</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tổng Hợp Exploration Quests</t>
+          <t>Tổng Hợp Nhiệm Vụ Thám Hiểm</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Exploring the Extreme Edge</t>
+          <t>Lahai-Roi: Khám Phá Vùng Biên Cực</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Exploring the Extreme Edge</t>
+          <t>Lahai-Roi: Khám Phá Vùng Biên Cực</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Khi Âm Vang Vô Định</t>
+          <t>Khi Những Âm Thanh Vô Định Vang Lên</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Act I</t>
+          <t>Hồi I</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Điều Gì Cháy Dưới Vùng Đất Băng Giá</t>
+          <t>Điều Gì Nung Nấu Dưới Lãnh Nguyên Băng Giá</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Act II</t>
+          <t>Hồi II</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Khúc Ca Sunrise Thứ Hai</t>
+          <t>Khúc Ca Bình Minh Thứ Hai</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Reconstruction Project</t>
+          <t>Dự Án Tái Cấu Trúc</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Chiến Dịch: Tái Thiết Biên Cương</t>
+          <t>Chiến dịch: Tái thiết Biên giới</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Expedition Project</t>
+          <t>Dự Án Thám Hiểm</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Đến Land Paradox</t>
+          <t>Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Jinzhou City Hall</t>
+          <t>Tòa Thị chính Jinzhou</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Leonidas Hotel Suite</t>
+          <t>Phòng Suite Khách sạn Leonidas</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Denia's Birthday Schedule</t>
+          <t>Lịch Trình Sinh Nhật Của Denia</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Happy Little Family</t>
+          <t>Gia đình nhỏ hạnh phúc</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Spacetrek Collective Early Warning Center</t>
+          <t>Trung Tâm Cảnh Báo Sớm Spacetrek Collective</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Lahai-Roi Route Network Office</t>
+          <t>Văn Phòng Mạng Lưới Tuyến Lahai-Roi</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Unnamed Sender</t>
+          <t>Người gửi ẩn danh</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Lightborne Horizons</t>
+          <t>Chân Trời Ánh Sáng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Academy News</t>
+          <t>Tin Tức Học Viện</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Spacetrek Convoy Transport Report</t>
+          <t>Báo cáo Vận chuyển Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Everything Startorch - Operations Department</t>
+          <t>Tất cả - Bộ phận Điều hành Startorch</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>A Ghi chú In the Book</t>
+          <t>Một Mảnh Giấy Trong Cuốn Sách</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Unsettling Device</t>
+          <t>Thiết Bị Đáng Ngờ</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Startorch Traffic Safety Regulations&lt;/b&gt;</t>
+          <t>&lt;b&gt;Quy Định An Toàn Giao Thông Startorch&lt;/b&gt;</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Bức Chụp ảnh Nhóm Dưới Ánh Mặt Trời New</t>
+          <t>Bức Ảnh Nhóm Dưới Ánh Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Bức Chụp ảnh Nhóm Dưới Ánh Mặt Trời New</t>
+          <t>Bức Ảnh Nhóm Dưới Ánh Mặt Trời Mới</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Startorch Academy Academic Affairs Hệ thống</t>
+          <t>Hệ thống Quản lý Học vụ Học viện Startorch</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Near Sundermere</t>
+          <t>Gần Sundermere</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Not long ago</t>
+          <t>Cách đây không lâu</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>At Startorch Academy</t>
+          <t>Tại Học viện Startorch</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>In Lynae's room</t>
+          <t>Trong phòng của Lynae</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Inside the Startorch Academy</t>
+          <t>Trong khuôn viên Startorch Academy</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Act III</t>
+          <t>Hồi III</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Ngôi Sao Hành Hương Xa</t>
+          <t>Ngôi Sao Viễn Du</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Act IV</t>
+          <t>Hồi IV</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Segue</t>
+          <t>Chuyển cảnh</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Thỏ phản chiếu trong Bóng tối</t>
+          <t>Rabbit Phản Chiếu Trong Kính</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
